--- a/top_10_per_region.xlsx
+++ b/top_10_per_region.xlsx
@@ -3902,27 +3902,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CEMAT.CO</t>
+          <t>REKA.HE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cemat A/S</t>
+          <t>Reka Industrial Oyj</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3931,53 +3931,57 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>32400001.64774966</v>
+        <v>28436282.94645024</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>UNRESEARCHED</t>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>-0.1157894901951926</v>
+        <v>0.0218977885840649</v>
       </c>
       <c r="L39" t="n">
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5329394697622627</v>
+        <v>0.5934770968995788</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4529985492979233</v>
+        <v>0.4154339678297052</v>
       </c>
       <c r="O39" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="P39" t="n">
-        <v>0.5462009200586186</v>
+        <v>0.5031643779205029</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.52</v>
+        <v>0.7</v>
       </c>
       <c r="R39" t="n">
         <v>5</v>
       </c>
       <c r="S39" t="n">
-        <v>0.7314337639298848</v>
+        <v>0.5091970866643191</v>
       </c>
       <c r="T39" t="n">
-        <v>0.447132317458232</v>
+        <v>0.516723941341706</v>
       </c>
       <c r="U39" t="n">
-        <v>0.8731808484081945</v>
+        <v>0.550802011622709</v>
       </c>
       <c r="V39" t="n">
-        <v>-0.1663226734073885</v>
+        <v>-5.998233215547703</v>
       </c>
       <c r="W39" t="n">
-        <v>0.49581</v>
-      </c>
-      <c r="X39" t="inlineStr"/>
+        <v>0.5739</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Operating thesis intact but Reka Pension Fund &lt;150 active members faces possible mandatory dissolution by 2028 if unresolved (disclosed)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3990,17 +3994,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>REKA.HE</t>
+          <t>SKAKO.CO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Reka Industrial Oyj</t>
+          <t>SKAKO A/S</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4010,7 +4014,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Electrical Equipment</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4019,57 +4023,53 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>28436282.94645024</v>
+        <v>5894950.449375451</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>YELLOW</t>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.0218977885840649</v>
+        <v>-0.3350328789631554</v>
       </c>
       <c r="L40" t="n">
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5934770968995788</v>
+        <v>0.4866378352163413</v>
       </c>
       <c r="N40" t="n">
-        <v>0.4154339678297052</v>
+        <v>0.4136421599338901</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="P40" t="n">
-        <v>0.5031643779205029</v>
+        <v>0.438548856785272</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.7</v>
+        <v>0.54</v>
       </c>
       <c r="R40" t="n">
         <v>5</v>
       </c>
       <c r="S40" t="n">
-        <v>0.5091970866643191</v>
+        <v>0.5</v>
       </c>
       <c r="T40" t="n">
-        <v>0.516723941341706</v>
+        <v>0.5351803653546787</v>
       </c>
       <c r="U40" t="n">
-        <v>0.550802011622709</v>
+        <v>0.1861472598399095</v>
       </c>
       <c r="V40" t="n">
-        <v>-5.998233215547703</v>
+        <v>33.21114050101136</v>
       </c>
       <c r="W40" t="n">
-        <v>0.5739</v>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>Operating thesis intact but Reka Pension Fund &lt;150 active members faces possible mandatory dissolution by 2028 if unresolved (disclosed)</t>
-        </is>
-      </c>
+        <v>0.54125</v>
+      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4082,82 +4082,86 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SKAKO.CO</t>
+          <t>GSF.OL</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SKAKO A/S</t>
+          <t>Grieg Seafood ASA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>Food &amp; Staples Retailing</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5894950.449375451</v>
+        <v>382407720.7129669</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>UNRESEARCHED</t>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>-0.3350328789631554</v>
+        <v>-0.0927344762279138</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4866378352163413</v>
+        <v>0.5795612672786915</v>
       </c>
       <c r="N41" t="n">
-        <v>0.4136421599338901</v>
+        <v>0.4056928870950841</v>
       </c>
       <c r="O41" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="P41" t="n">
-        <v>0.438548856785272</v>
+        <v>0.4798446607566899</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="R41" t="n">
         <v>5</v>
       </c>
       <c r="S41" t="n">
-        <v>0.5</v>
+        <v>0.5320476562102132</v>
       </c>
       <c r="T41" t="n">
-        <v>0.5351803653546787</v>
+        <v>0.3347074237721578</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1861472598399095</v>
+        <v>0.8078003786381953</v>
       </c>
       <c r="V41" t="n">
-        <v>33.21114050101136</v>
+        <v>-5.865620620661164</v>
       </c>
       <c r="W41" t="n">
-        <v>0.54125</v>
-      </c>
-      <c r="X41" t="inlineStr"/>
+        <v>0.6666800000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Cermaq filed $24m claim against Grieg over divestment closed Dec 2025; material lawsuit overhang on NOK 4bn shareholder-return plan</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -13532,27 +13536,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CEMAT.CO</t>
+          <t>REKA.HE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cemat A/S</t>
+          <t>Reka Industrial Oyj</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -13561,53 +13565,57 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>32400001.64774966</v>
+        <v>28436282.94645024</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>UNRESEARCHED</t>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-0.1157894901951926</v>
+        <v>0.0218977885840649</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5329394697622627</v>
+        <v>0.5934770968995788</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4529985492979233</v>
+        <v>0.4154339678297052</v>
       </c>
       <c r="O9" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5462009200586186</v>
+        <v>0.5031643779205029</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.52</v>
+        <v>0.7</v>
       </c>
       <c r="R9" t="n">
         <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7314337639298848</v>
+        <v>0.5091970866643191</v>
       </c>
       <c r="T9" t="n">
-        <v>0.447132317458232</v>
+        <v>0.516723941341706</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8731808484081945</v>
+        <v>0.550802011622709</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1663226734073885</v>
+        <v>-5.998233215547703</v>
       </c>
       <c r="W9" t="n">
-        <v>0.49581</v>
-      </c>
-      <c r="X9" t="inlineStr"/>
+        <v>0.5739</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Operating thesis intact but Reka Pension Fund &lt;150 active members faces possible mandatory dissolution by 2028 if unresolved (disclosed)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13620,17 +13628,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>REKA.HE</t>
+          <t>SKAKO.CO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Reka Industrial Oyj</t>
+          <t>SKAKO A/S</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -13640,7 +13648,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Electrical Equipment</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -13649,57 +13657,53 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>28436282.94645024</v>
+        <v>5894950.449375451</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>YELLOW</t>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.0218977885840649</v>
+        <v>-0.3350328789631554</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5934770968995788</v>
+        <v>0.4866378352163413</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4154339678297052</v>
+        <v>0.4136421599338901</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5031643779205029</v>
+        <v>0.438548856785272</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7</v>
+        <v>0.54</v>
       </c>
       <c r="R10" t="n">
         <v>5</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5091970866643191</v>
+        <v>0.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0.516723941341706</v>
+        <v>0.5351803653546787</v>
       </c>
       <c r="U10" t="n">
-        <v>0.550802011622709</v>
+        <v>0.1861472598399095</v>
       </c>
       <c r="V10" t="n">
-        <v>-5.998233215547703</v>
+        <v>33.21114050101136</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5739</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Operating thesis intact but Reka Pension Fund &lt;150 active members faces possible mandatory dissolution by 2028 if unresolved (disclosed)</t>
-        </is>
-      </c>
+        <v>0.54125</v>
+      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13712,82 +13716,86 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SKAKO.CO</t>
+          <t>GSF.OL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SKAKO A/S</t>
+          <t>Grieg Seafood ASA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>Food &amp; Staples Retailing</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5894950.449375451</v>
+        <v>382407720.7129669</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>UNRESEARCHED</t>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-0.3350328789631554</v>
+        <v>-0.0927344762279138</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4866378352163413</v>
+        <v>0.5795612672786915</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4136421599338901</v>
+        <v>0.4056928870950841</v>
       </c>
       <c r="O11" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="P11" t="n">
-        <v>0.438548856785272</v>
+        <v>0.4798446607566899</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="R11" t="n">
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5</v>
+        <v>0.5320476562102132</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5351803653546787</v>
+        <v>0.3347074237721578</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1861472598399095</v>
+        <v>0.8078003786381953</v>
       </c>
       <c r="V11" t="n">
-        <v>33.21114050101136</v>
+        <v>-5.865620620661164</v>
       </c>
       <c r="W11" t="n">
-        <v>0.54125</v>
-      </c>
-      <c r="X11" t="inlineStr"/>
+        <v>0.6666800000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Cermaq filed $24m claim against Grieg over divestment closed Dec 2025; material lawsuit overhang on NOK 4bn shareholder-return plan</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
